--- a/artfynd/A 57809-2025 artfynd.xlsx
+++ b/artfynd/A 57809-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109909957</v>
+        <v>112610306</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>774069.790008735</v>
+        <v>774070</v>
       </c>
       <c r="R2" t="n">
-        <v>7357024.504640547</v>
+        <v>7357025</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -789,113 +774,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>112610306</v>
-      </c>
-      <c r="B3" t="n">
-        <v>89791</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Porodaedalea pini</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Lakaträsk, Nb</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>774070</v>
-      </c>
-      <c r="R3" t="n">
-        <v>7357025</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Edefors</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
